--- a/12620172.xlsx
+++ b/12620172.xlsx
@@ -5,10 +5,10 @@
   <workbookPr/>
   <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
     <mc:Choice Requires="x15">
-      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="https://d.docs.live.net/68ec2164436ee122/Desktop/"/>
+      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="https://d.docs.live.net/68ec2164436ee122/Desktop/GIT/CAP776/"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="16" documentId="8_{0D51F7DB-0C06-426F-86F8-F73CBDB8B9A2}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{BDBA7949-9A8F-4E8F-8596-C69588EB0C55}"/>
+  <xr:revisionPtr revIDLastSave="17" documentId="8_{0D51F7DB-0C06-426F-86F8-F73CBDB8B9A2}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{99E78C4D-60A8-4F04-A323-8509DB05E70A}"/>
   <bookViews>
     <workbookView xWindow="-110" yWindow="-110" windowWidth="19420" windowHeight="10300" tabRatio="500" activeTab="1" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
@@ -1162,7 +1162,9 @@
         <v>480</v>
       </c>
       <c r="C10" s="14"/>
-      <c r="D10" s="14"/>
+      <c r="D10" s="14">
+        <v>350</v>
+      </c>
       <c r="E10" s="14"/>
       <c r="F10" s="14">
         <v>240</v>
@@ -1173,11 +1175,11 @@
       <c r="H10" s="14"/>
       <c r="I10" s="15">
         <f t="shared" si="0"/>
-        <v>720</v>
+        <v>1070</v>
       </c>
       <c r="J10" s="15">
         <f t="shared" si="1"/>
-        <v>720</v>
+        <v>370</v>
       </c>
       <c r="K10" s="16" t="s">
         <v>49</v>

--- a/12620172.xlsx
+++ b/12620172.xlsx
@@ -5,10 +5,10 @@
   <workbookPr/>
   <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
     <mc:Choice Requires="x15">
-      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="https://d.docs.live.net/68ec2164436ee122/Desktop/GIT/CAP776/"/>
+      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="https://d.docs.live.net/68ec2164436ee122/Desktop/"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="17" documentId="8_{0D51F7DB-0C06-426F-86F8-F73CBDB8B9A2}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{99E78C4D-60A8-4F04-A323-8509DB05E70A}"/>
+  <xr:revisionPtr revIDLastSave="17" documentId="8_{0D51F7DB-0C06-426F-86F8-F73CBDB8B9A2}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{C843D5C8-1FDE-45FF-A63F-DD10B55DB8BE}"/>
   <bookViews>
     <workbookView xWindow="-110" yWindow="-110" windowWidth="19420" windowHeight="10300" tabRatio="500" activeTab="1" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
@@ -26,7 +26,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="60" uniqueCount="58">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="64" uniqueCount="62">
   <si>
     <t>My Data, My Code</t>
   </si>
@@ -219,6 +219,18 @@
   </si>
   <si>
     <t>Average</t>
+  </si>
+  <si>
+    <t>Bad, because today my health is not well</t>
+  </si>
+  <si>
+    <t>Nothing special</t>
+  </si>
+  <si>
+    <t>Low</t>
+  </si>
+  <si>
+    <t>Today I notice myself and learn what is the right way of self study.</t>
   </si>
 </sst>
 </file>
@@ -1110,8 +1122,12 @@
       <c r="E8" s="14">
         <v>30</v>
       </c>
-      <c r="F8" s="14"/>
-      <c r="G8" s="14"/>
+      <c r="F8" s="14">
+        <v>0</v>
+      </c>
+      <c r="G8" s="14">
+        <v>0</v>
+      </c>
       <c r="H8" s="14"/>
       <c r="I8" s="15">
         <f t="shared" si="0"/>
@@ -1163,14 +1179,16 @@
       </c>
       <c r="C10" s="14"/>
       <c r="D10" s="14">
+        <v>200</v>
+      </c>
+      <c r="E10" s="14">
+        <v>40</v>
+      </c>
+      <c r="F10" s="14">
         <v>350</v>
       </c>
-      <c r="E10" s="14"/>
-      <c r="F10" s="14">
-        <v>240</v>
-      </c>
       <c r="G10" s="14">
-        <v>4</v>
+        <v>7</v>
       </c>
       <c r="H10" s="14"/>
       <c r="I10" s="15">
@@ -1192,30 +1210,52 @@
       </c>
       <c r="N10" s="17"/>
     </row>
-    <row r="11" spans="1:14" x14ac:dyDescent="0.35">
-      <c r="A11" s="13"/>
-      <c r="B11" s="14"/>
+    <row r="11" spans="1:14" ht="58" x14ac:dyDescent="0.35">
+      <c r="A11" s="13">
+        <v>46259</v>
+      </c>
+      <c r="B11" s="14">
+        <v>480</v>
+      </c>
       <c r="C11" s="14"/>
-      <c r="D11" s="14"/>
-      <c r="E11" s="14"/>
-      <c r="F11" s="14"/>
-      <c r="G11" s="14"/>
+      <c r="D11" s="14">
+        <v>210</v>
+      </c>
+      <c r="E11" s="14">
+        <v>40</v>
+      </c>
+      <c r="F11" s="14">
+        <v>350</v>
+      </c>
+      <c r="G11" s="14">
+        <v>7</v>
+      </c>
       <c r="H11" s="14"/>
-      <c r="I11" s="15" t="str">
+      <c r="I11" s="15">
         <f t="shared" si="0"/>
-        <v/>
-      </c>
-      <c r="J11" s="15" t="str">
+        <v>1080</v>
+      </c>
+      <c r="J11" s="15">
         <f t="shared" si="1"/>
-        <v/>
-      </c>
-      <c r="K11" s="16"/>
-      <c r="L11" s="16"/>
-      <c r="M11" s="16"/>
-      <c r="N11" s="17"/>
+        <v>360</v>
+      </c>
+      <c r="K11" s="16" t="s">
+        <v>58</v>
+      </c>
+      <c r="L11" s="16" t="s">
+        <v>59</v>
+      </c>
+      <c r="M11" s="16" t="s">
+        <v>60</v>
+      </c>
+      <c r="N11" s="17" t="s">
+        <v>61</v>
+      </c>
     </row>
     <row r="12" spans="1:14" x14ac:dyDescent="0.35">
-      <c r="A12" s="13"/>
+      <c r="A12" s="13">
+        <v>46260</v>
+      </c>
       <c r="B12" s="14"/>
       <c r="C12" s="14"/>
       <c r="D12" s="14"/>
@@ -1237,7 +1277,9 @@
       <c r="N12" s="17"/>
     </row>
     <row r="13" spans="1:14" x14ac:dyDescent="0.35">
-      <c r="A13" s="13"/>
+      <c r="A13" s="13">
+        <v>46261</v>
+      </c>
       <c r="B13" s="14"/>
       <c r="C13" s="14"/>
       <c r="D13" s="14"/>
@@ -1259,7 +1301,9 @@
       <c r="N13" s="17"/>
     </row>
     <row r="14" spans="1:14" x14ac:dyDescent="0.35">
-      <c r="A14" s="13"/>
+      <c r="A14" s="13">
+        <v>46262</v>
+      </c>
       <c r="B14" s="14"/>
       <c r="C14" s="14"/>
       <c r="D14" s="14"/>

--- a/12620172.xlsx
+++ b/12620172.xlsx
@@ -5,10 +5,10 @@
   <workbookPr/>
   <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
     <mc:Choice Requires="x15">
-      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="https://d.docs.live.net/68ec2164436ee122/Desktop/"/>
+      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="https://d.docs.live.net/68ec2164436ee122/Desktop/PYTHON/CAP776/"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="17" documentId="8_{0D51F7DB-0C06-426F-86F8-F73CBDB8B9A2}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{C843D5C8-1FDE-45FF-A63F-DD10B55DB8BE}"/>
+  <xr:revisionPtr revIDLastSave="18" documentId="8_{0D51F7DB-0C06-426F-86F8-F73CBDB8B9A2}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{CB454112-B5A7-4480-97A8-36977C7BADF6}"/>
   <bookViews>
     <workbookView xWindow="-110" yWindow="-110" windowWidth="19420" windowHeight="10300" tabRatio="500" activeTab="1" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
@@ -1285,7 +1285,9 @@
       <c r="D13" s="14"/>
       <c r="E13" s="14"/>
       <c r="F13" s="14"/>
-      <c r="G13" s="14"/>
+      <c r="G13" s="14">
+        <v>4</v>
+      </c>
       <c r="H13" s="14"/>
       <c r="I13" s="15" t="str">
         <f t="shared" si="0"/>

--- a/12620172.xlsx
+++ b/12620172.xlsx
@@ -8,7 +8,7 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="https://d.docs.live.net/68ec2164436ee122/Desktop/PYTHON/CAP776/"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="18" documentId="8_{0D51F7DB-0C06-426F-86F8-F73CBDB8B9A2}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{CB454112-B5A7-4480-97A8-36977C7BADF6}"/>
+  <xr:revisionPtr revIDLastSave="32" documentId="8_{0D51F7DB-0C06-426F-86F8-F73CBDB8B9A2}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{A0B28D8D-F904-4773-9B0B-37EEE82A038F}"/>
   <bookViews>
     <workbookView xWindow="-110" yWindow="-110" windowWidth="19420" windowHeight="10300" tabRatio="500" activeTab="1" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
@@ -26,7 +26,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="64" uniqueCount="62">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="81" uniqueCount="62">
   <si>
     <t>My Data, My Code</t>
   </si>
@@ -218,19 +218,19 @@
     <t>AUGUST</t>
   </si>
   <si>
-    <t>Average</t>
-  </si>
-  <si>
-    <t>Bad, because today my health is not well</t>
-  </si>
-  <si>
-    <t>Nothing special</t>
-  </si>
-  <si>
     <t>Low</t>
   </si>
   <si>
     <t>Today I notice myself and learn what is the right way of self study.</t>
+  </si>
+  <si>
+    <t>Neutral</t>
+  </si>
+  <si>
+    <t>High</t>
+  </si>
+  <si>
+    <t>Excellent</t>
   </si>
 </sst>
 </file>
@@ -1103,9 +1103,15 @@
         <f t="shared" si="1"/>
         <v>580</v>
       </c>
-      <c r="K7" s="16"/>
-      <c r="L7" s="16"/>
-      <c r="M7" s="16"/>
+      <c r="K7" s="16" t="s">
+        <v>49</v>
+      </c>
+      <c r="L7" s="16" t="s">
+        <v>59</v>
+      </c>
+      <c r="M7" s="16" t="s">
+        <v>51</v>
+      </c>
       <c r="N7" s="17"/>
     </row>
     <row r="8" spans="1:14" x14ac:dyDescent="0.35">
@@ -1137,9 +1143,15 @@
         <f t="shared" si="1"/>
         <v>690</v>
       </c>
-      <c r="K8" s="16"/>
-      <c r="L8" s="16"/>
-      <c r="M8" s="16"/>
+      <c r="K8" s="16" t="s">
+        <v>59</v>
+      </c>
+      <c r="L8" s="16" t="s">
+        <v>59</v>
+      </c>
+      <c r="M8" s="16" t="s">
+        <v>51</v>
+      </c>
       <c r="N8" s="17"/>
     </row>
     <row r="9" spans="1:14" x14ac:dyDescent="0.35">
@@ -1165,9 +1177,15 @@
         <f t="shared" si="1"/>
         <v>780</v>
       </c>
-      <c r="K9" s="16"/>
-      <c r="L9" s="16"/>
-      <c r="M9" s="16"/>
+      <c r="K9" s="16" t="s">
+        <v>59</v>
+      </c>
+      <c r="L9" s="16" t="s">
+        <v>50</v>
+      </c>
+      <c r="M9" s="16" t="s">
+        <v>60</v>
+      </c>
       <c r="N9" s="17"/>
     </row>
     <row r="10" spans="1:14" x14ac:dyDescent="0.35">
@@ -1206,11 +1224,11 @@
         <v>50</v>
       </c>
       <c r="M10" s="16" t="s">
-        <v>57</v>
+        <v>51</v>
       </c>
       <c r="N10" s="17"/>
     </row>
-    <row r="11" spans="1:14" ht="58" x14ac:dyDescent="0.35">
+    <row r="11" spans="1:14" x14ac:dyDescent="0.35">
       <c r="A11" s="13">
         <v>46259</v>
       </c>
@@ -1239,113 +1257,167 @@
         <f t="shared" si="1"/>
         <v>360</v>
       </c>
-      <c r="K11" s="16" t="s">
-        <v>58</v>
-      </c>
-      <c r="L11" s="16" t="s">
-        <v>59</v>
-      </c>
-      <c r="M11" s="16" t="s">
-        <v>60</v>
-      </c>
-      <c r="N11" s="17" t="s">
-        <v>61</v>
-      </c>
-    </row>
-    <row r="12" spans="1:14" x14ac:dyDescent="0.35">
+      <c r="K11" s="16"/>
+      <c r="L11" s="16"/>
+      <c r="M11" s="16"/>
+      <c r="N11" s="17"/>
+    </row>
+    <row r="12" spans="1:14" ht="43.5" x14ac:dyDescent="0.35">
       <c r="A12" s="13">
         <v>46260</v>
       </c>
-      <c r="B12" s="14"/>
+      <c r="B12" s="14">
+        <v>480</v>
+      </c>
       <c r="C12" s="14"/>
-      <c r="D12" s="14"/>
-      <c r="E12" s="14"/>
-      <c r="F12" s="14"/>
-      <c r="G12" s="14"/>
+      <c r="D12" s="14">
+        <v>210</v>
+      </c>
+      <c r="E12" s="14">
+        <v>40</v>
+      </c>
+      <c r="F12" s="14">
+        <v>350</v>
+      </c>
+      <c r="G12" s="14">
+        <v>7</v>
+      </c>
       <c r="H12" s="14"/>
-      <c r="I12" s="15" t="str">
+      <c r="I12" s="15">
         <f t="shared" si="0"/>
-        <v/>
-      </c>
-      <c r="J12" s="15" t="str">
+        <v>1080</v>
+      </c>
+      <c r="J12" s="15">
         <f t="shared" si="1"/>
-        <v/>
-      </c>
-      <c r="K12" s="16"/>
-      <c r="L12" s="16"/>
-      <c r="M12" s="16"/>
-      <c r="N12" s="17"/>
+        <v>360</v>
+      </c>
+      <c r="K12" s="16" t="s">
+        <v>57</v>
+      </c>
+      <c r="L12" s="16" t="s">
+        <v>59</v>
+      </c>
+      <c r="M12" s="16" t="s">
+        <v>57</v>
+      </c>
+      <c r="N12" s="17" t="s">
+        <v>58</v>
+      </c>
     </row>
     <row r="13" spans="1:14" x14ac:dyDescent="0.35">
       <c r="A13" s="13">
         <v>46261</v>
       </c>
-      <c r="B13" s="14"/>
+      <c r="B13" s="14">
+        <v>480</v>
+      </c>
       <c r="C13" s="14"/>
-      <c r="D13" s="14"/>
-      <c r="E13" s="14"/>
-      <c r="F13" s="14"/>
+      <c r="D13" s="14">
+        <v>210</v>
+      </c>
+      <c r="E13" s="14">
+        <v>40</v>
+      </c>
+      <c r="F13" s="14">
+        <v>240</v>
+      </c>
       <c r="G13" s="14">
         <v>4</v>
       </c>
       <c r="H13" s="14"/>
-      <c r="I13" s="15" t="str">
+      <c r="I13" s="15">
         <f t="shared" si="0"/>
-        <v/>
-      </c>
-      <c r="J13" s="15" t="str">
+        <v>970</v>
+      </c>
+      <c r="J13" s="15">
         <f t="shared" si="1"/>
-        <v/>
-      </c>
-      <c r="K13" s="16"/>
-      <c r="L13" s="16"/>
-      <c r="M13" s="16"/>
+        <v>470</v>
+      </c>
+      <c r="K13" s="16" t="s">
+        <v>49</v>
+      </c>
+      <c r="L13" s="16" t="s">
+        <v>50</v>
+      </c>
+      <c r="M13" s="16" t="s">
+        <v>60</v>
+      </c>
       <c r="N13" s="17"/>
     </row>
     <row r="14" spans="1:14" x14ac:dyDescent="0.35">
       <c r="A14" s="13">
         <v>46262</v>
       </c>
-      <c r="B14" s="14"/>
+      <c r="B14" s="14">
+        <v>480</v>
+      </c>
       <c r="C14" s="14"/>
-      <c r="D14" s="14"/>
-      <c r="E14" s="14"/>
-      <c r="F14" s="14"/>
-      <c r="G14" s="14"/>
+      <c r="D14" s="14">
+        <v>210</v>
+      </c>
+      <c r="E14" s="14">
+        <v>40</v>
+      </c>
+      <c r="F14" s="14">
+        <v>180</v>
+      </c>
+      <c r="G14" s="14">
+        <v>3</v>
+      </c>
       <c r="H14" s="14"/>
-      <c r="I14" s="15" t="str">
+      <c r="I14" s="15">
         <f t="shared" si="0"/>
-        <v/>
-      </c>
-      <c r="J14" s="15" t="str">
+        <v>910</v>
+      </c>
+      <c r="J14" s="15">
         <f t="shared" si="1"/>
-        <v/>
-      </c>
-      <c r="K14" s="16"/>
-      <c r="L14" s="16"/>
+        <v>530</v>
+      </c>
+      <c r="K14" s="16" t="s">
+        <v>61</v>
+      </c>
+      <c r="L14" s="16" t="s">
+        <v>50</v>
+      </c>
       <c r="M14" s="16"/>
       <c r="N14" s="17"/>
     </row>
     <row r="15" spans="1:14" x14ac:dyDescent="0.35">
-      <c r="A15" s="13"/>
+      <c r="A15" s="13">
+        <v>46263</v>
+      </c>
       <c r="B15" s="14"/>
       <c r="C15" s="14"/>
-      <c r="D15" s="14"/>
-      <c r="E15" s="14"/>
-      <c r="F15" s="14"/>
-      <c r="G15" s="14"/>
+      <c r="D15" s="14">
+        <v>300</v>
+      </c>
+      <c r="E15" s="14">
+        <v>40</v>
+      </c>
+      <c r="F15" s="14">
+        <v>0</v>
+      </c>
+      <c r="G15" s="14">
+        <v>0</v>
+      </c>
       <c r="H15" s="14"/>
-      <c r="I15" s="15" t="str">
+      <c r="I15" s="15">
         <f t="shared" si="0"/>
-        <v/>
-      </c>
-      <c r="J15" s="15" t="str">
+        <v>340</v>
+      </c>
+      <c r="J15" s="15">
         <f t="shared" si="1"/>
-        <v/>
-      </c>
-      <c r="K15" s="16"/>
-      <c r="L15" s="16"/>
-      <c r="M15" s="16"/>
+        <v>1100</v>
+      </c>
+      <c r="K15" s="16" t="s">
+        <v>49</v>
+      </c>
+      <c r="L15" s="16" t="s">
+        <v>59</v>
+      </c>
+      <c r="M15" s="16" t="s">
+        <v>57</v>
+      </c>
       <c r="N15" s="17"/>
     </row>
     <row r="16" spans="1:14" x14ac:dyDescent="0.35">
